--- a/artfynd/A 60557-2025 artfynd.xlsx
+++ b/artfynd/A 60557-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>58220436</v>
+        <v>128516739</v>
       </c>
       <c r="B2" t="n">
-        <v>101680</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91334</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,37 +686,46 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>222412</v>
+        <v>2009</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Rödbrun jordstjärna</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Geastrum rufescens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>Pers.:Pers.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Stockebäcksäng 5550/6450, Nrk</t>
+          <t>Skogstorp, Skogstorp, Nrk</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>532551.020197916</v>
+        <v>532537</v>
       </c>
       <c r="R2" t="n">
-        <v>6553673.058167812</v>
+        <v>6553738</v>
       </c>
       <c r="S2" t="n">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,27 +749,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>1982-04-21</t>
+          <t>2025-09-18</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>1982-04-21</t>
+          <t>2025-09-18</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Flera</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -777,20 +776,15 @@
       <c r="AG2" t="b">
         <v>0</v>
       </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Gunnar Hallin</t>
+          <t>Magnus Friberg</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Gunnar Hallin</t>
+          <t>Magnus Friberg</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
@@ -800,7 +794,7 @@
         <v>129385645</v>
       </c>
       <c r="B3" t="n">
-        <v>91031</v>
+        <v>91334</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -910,6 +904,113 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>58220436</v>
+      </c>
+      <c r="B4" t="n">
+        <v>104628</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>222412</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Tibast</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Daphne mezereum</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Stockebäcksäng 5550/6450, Nrk</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>532551</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6553673</v>
+      </c>
+      <c r="S4" t="n">
+        <v>50</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Asker</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>1982-04-21</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>1982-04-21</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Flera</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Gunnar Hallin</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Gunnar Hallin</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
